--- a/ressources/tableaux-de-travail/v2/GT_Dessertes_Tab_PointsEau_V2.xlsx
+++ b/ressources/tableaux-de-travail/v2/GT_Dessertes_Tab_PointsEau_V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WS\zz_telechargement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ignf.sharepoint.com/sites/Naviforest/Documents partages/General/Tranche 3/04. Standard Dessertes en forêt  Transport de bois et DFCI/Tableaux de travail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7B9D383D-6FF5-4AEE-B904-6084921D0211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7051EBBA-96A4-4BD3-A0BF-611581345669}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{7B9D383D-6FF5-4AEE-B904-6084921D0211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{338E0D7D-092E-42A3-8AE4-7E615FAA6A16}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard AFIGEO" sheetId="5" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="table_V1etV2" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">table_V1etV2!$A$2:$R$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'standard AFIGEO_V1'!$A$2:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">table_V1etV2!$A$2:$S$36</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="224">
   <si>
     <t>Nom du champ</t>
   </si>
@@ -470,34 +468,16 @@
     <t>Réponse/commentaire fait pendant le GT du 16/01/2026</t>
   </si>
   <si>
-    <t>Nom en francais</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
-    <t>Code INSEE (BD TOPO)</t>
-  </si>
-  <si>
     <t>BD TOPO</t>
   </si>
   <si>
-    <t>Raccord BD TOPO</t>
-  </si>
-  <si>
     <t>identifiant BD TOPO (à faire évoluer)</t>
   </si>
   <si>
     <t>Laisser vide, identifiant créé automatiquement lors de la première intégration à la BD TOPO</t>
-  </si>
-  <si>
-    <t>Identifiant BD TOPO</t>
-  </si>
-  <si>
-    <t>identifiant créé automatiquement lors de la première intégration à la BD TOPO (Laisser vide si l'objet n'a pas encore été remonté dans la BD TOPO)</t>
   </si>
   <si>
     <t>Optionnel</t>
@@ -514,13 +494,7 @@
     <t>Numéro ou référence du PEI</t>
   </si>
   <si>
-    <t>num_PEI</t>
-  </si>
-  <si>
     <t>alphanumérique</t>
-  </si>
-  <si>
-    <t>Numéro de référence du PEI validé en interservices. Il fortement recommandé d'indiquer ici l'identifiant SDIS du PEI s'il existe.</t>
   </si>
   <si>
     <t>validé par le GT</t>
@@ -530,13 +504,7 @@
 Conserver tel quel mais en Optionnel</t>
   </si>
   <si>
-    <t>Numéro Gestionnaire</t>
-  </si>
-  <si>
     <t>ref_gestion</t>
-  </si>
-  <si>
-    <t>Numéro interne du PEI pour le gestionnaire.</t>
   </si>
   <si>
     <t>Nom du gestionnaire du PEI (information anonymisée)</t>
@@ -557,16 +525,6 @@
   </si>
   <si>
     <t>Liste</t>
-  </si>
-  <si>
-    <t>Type de point d’eau incendie. La typologie issue du règlement national DECI et est évolutive si le réglement change.</t>
-  </si>
-  <si>
-    <t>- PI (Poteau d’Incendie), 
-- BI (Prise d’eau sous pression, notamment bouche d’incendie), 
-- PA (Point d’aspiration aménagé), 
-- CI (Citerne aérienne ou enterrée)
-- Autre</t>
   </si>
   <si>
     <t>Liste à retravailler par le GT</t>
@@ -592,20 +550,6 @@
     <t xml:space="preserve">Précision sur le type de point d’eau incendie </t>
   </si>
   <si>
-    <t>- Points d’eau naturels ou artificiels
-- Points de puisage
-- Réseaux d’irrigation agricoles
-- Autres réseaux d’eau sous pression
-- Citernes enterrées, bâches à eau, citernes aériennes et autres réserves fixes
-- plan_eau
-- piscine
-- puits 
-- cours_eau
-- Forage DFCI
-- forage agricole (mettre les deux si la distinction ne peut pas se faire plus loin)
-- Autres dispositifs</t>
-  </si>
-  <si>
     <t>Ne rentre pas dans le cadre de notre standard
 Attribut non conservé</t>
   </si>
@@ -620,10 +564,6 @@
 </t>
   </si>
   <si>
-    <t>- public
-- privé</t>
-  </si>
-  <si>
     <t>Donnée trop sensible pour être remontée au niveau national</t>
   </si>
   <si>
@@ -635,9 +575,6 @@
 </t>
   </si>
   <si>
-    <t>Attester l'absence de besoin dans le standard</t>
-  </si>
-  <si>
     <t>Capacité volumique utile de la source d’eau en m3. Si la source est inépuisable, mettre 9999.</t>
   </si>
   <si>
@@ -651,12 +588,6 @@
 Pour l'IGN, besoin de la méthode et ils déduisent </t>
   </si>
   <si>
-    <t>Methode d'acquisition</t>
-  </si>
-  <si>
-    <t>Liste dans la BD TOPO</t>
-  </si>
-  <si>
     <t xml:space="preserve">calculé directement, pas besoin de l'indiquer dans le standard
 </t>
   </si>
@@ -673,23 +604,12 @@
     <t>access_hbe</t>
   </si>
   <si>
-    <t>Défini l'accessibilité du point par un HBE</t>
-  </si>
-  <si>
-    <t>- Léger 
-- Lourd
-- Non accessible (selon le type, peut rendre ce champ remplissable ou pas)</t>
-  </si>
-  <si>
     <t>perenne/non perenne</t>
   </si>
   <si>
     <t>Liste dans BD TOPO, récupérer tele champ</t>
   </si>
   <si>
-    <t>Persistance (voir BD TOPO)</t>
-  </si>
-  <si>
     <t>autres ressources en eau = eau potable de reserve/ressources naturelles</t>
   </si>
   <si>
@@ -706,13 +626,187 @@
   </si>
   <si>
     <t>Pas de besoin supplémentaires remontés par le GT durant la séance</t>
+  </si>
+  <si>
+    <t>Commentaire GIP ATGeRi 04/02/2026</t>
+  </si>
+  <si>
+    <t>Reponse IGN 18/02/2026</t>
+  </si>
+  <si>
+    <t>Code INSEE de la commune</t>
+  </si>
+  <si>
+    <t>INSEE_COM</t>
+  </si>
+  <si>
+    <t>Texte (5 caractères)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommandation </t>
+  </si>
+  <si>
+    <t>Il est très fortement recommandé de remplir ce champ. En cas de relation sémantique avec la table tronçon, le lien s'effectue sur cet ID.</t>
+  </si>
+  <si>
+    <t>Le code INSEE est calculé d'après l'emprise de la commune.</t>
+  </si>
+  <si>
+    <t>Identifiant de l'objet</t>
+  </si>
+  <si>
+    <t>Identifiant unique du point d'eau</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Nom de l'attribut</t>
+  </si>
+  <si>
+    <t>Nom de l'élément dans la BD TOPO (nouveau noms comme nouvelle table)(n'apparaîtra que dans la table de correspondance)</t>
+  </si>
+  <si>
+    <t>Saisie contributeur</t>
+  </si>
+  <si>
+    <t>ref_PEI</t>
+  </si>
+  <si>
+    <t>Numéro ou référence interne du PEI pour le gestionnaire</t>
+  </si>
+  <si>
+    <t>Numéro ou référence du point d’eau visible sur le terrain</t>
+  </si>
+  <si>
+    <t>Type de point d’eau incendie. La typologie est issue du règlement national DECI et est évolutive si le réglement change.</t>
+  </si>
+  <si>
+    <t>à valider</t>
+  </si>
+  <si>
+    <t>conserve l'attribut en optionnel</t>
+  </si>
+  <si>
+    <t>ok en facultatif ; mais attention, le champ débit n'a pas été commenté, alors que les 2 champs (débit et pression) vont de paire ; donc appliquer le même fonctionnement dans le standard pour les 2
+&gt;&gt; conserve l'attribut en optionnel</t>
+  </si>
+  <si>
+    <t>Concernant la pression à 1bar, cela fait partie du modèle de données AFIGEO donc je trouve cela vraiment trop dommage de ne pas garder cette information. C’est une information cruciale pour savoir le type de risque couvert par un PEI.
+https://schema.data.gouv.fr/datakode/schema-pei/1.0.1/documentation.html#valeur-de-debit-mesure-exprime-en-m3-h-sous-une-pression-de-1-bar-propriete-debit
+A la rigueur, vous pouvez laisser ce champ en facultatif si cela pose problème à certains de compléter cette information.
++ validation Amélie Pinaud (SDIS17)
+ &gt;&gt; conserve l'attribut en optionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persistance </t>
+  </si>
+  <si>
+    <t>Intermittent | Permanent</t>
+  </si>
+  <si>
+    <t>Degré de persistance de l'écoulement de l'eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méthode d'acquisition </t>
+  </si>
+  <si>
+    <t>methode_d_acquisition_planimetrique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liste </t>
+  </si>
+  <si>
+    <t>Méthode principale ayant permis d'acquérir la géométrie planimétrique de l'objet. La méthode d’acquisition fait référence :
+- soit aux types de sources (Orthophotographie par exemple),
+- soit au processus (Photogrammétrie par exemple),
+- soit aux anciennes bases de données.
+L’objectif de cet attribut est de fournir une estimation de la précision de la géométrie de l’objet.</t>
+  </si>
+  <si>
+    <t>BDCarto | BDNyme | BDParcellaire | BDParcellaire recalée | BDTopo | Calcul d'enveloppe urbaine | Calculé | Fichier numérique décimétrique | Fichier numérique métrique | Fichier numérique non métrique | Géocodage | Géoroute | Image satellite | Image satellite HR | Inconnue | Levé GPS | Levé non GPS | Lidar | Lidar HD | Orthophotographie | Photogrammétrie | Plan métrique papier | Plan non métrique papier | Processus IA métrique | Processus IA non métrique | Scan25</t>
+  </si>
+  <si>
+    <t>La liste exhaustive et son détail sont retrouvables dans les spécifications de la BD TOPO : https://bdtopoexplorer.ign.fr/</t>
+  </si>
+  <si>
+    <t>BD TOPO, Saisie contributeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code INSEE de la commune sur laquelle se situe le ponctuel
+</t>
+  </si>
+  <si>
+    <t>Numéro ou référence du PEI validé en interservices. S'il existe, il fortement recommandé d'utiliser l'identifiant SDIS du PEI pour remplir ce champ.</t>
+  </si>
+  <si>
+    <t>Numéro ou référence pour le gestionnaire</t>
+  </si>
+  <si>
+    <t>Commentaire de Nicolas GODELU 22/01/2026</t>
+  </si>
+  <si>
+    <t>- Poteau d’Incendie
+- Bouche d’incendie
+- Point d’aspiration aménagé
+- Citerne aérienne ou enterrée
+- Autre</t>
+  </si>
+  <si>
+    <t>- Point d’eau naturel ou artificiel
+- Point de puisage
+- Réseau d’irrigation agricole
+- Autre réseau d’eau sous pression
+- Citerne enterrée
+- Citerne aérienne 
+- Bâche à eau
+- Plan d'eau
+- Piscine
+- Puits
+- Cours d'eau
+- Forage DFCI
+- Forage agricole
+- Forage industriel
+- Autre dispositif</t>
+  </si>
+  <si>
+    <t>Pourquoi "citernes enterrées, bâches à eau, citernes aériennes et autres réserves fixes" alors qu'il y a "type_pei" = "CI" ? 
+&gt;&gt; séparation des valeurs pour une meilleur précision &gt; ok?
+Redondance entre "plan_eau" et "points d'eau naturels ou artificiels" 
+&gt;&gt; besoin de la valeur plan d'eau? Il y a besoin deséparation entre point d'eau naturel et point d'eau artificiel?
+Merci d'ajouter "Forage industriel" (à différencier de "Forage DFCI" et "Forage agricole")
+&gt;&gt; ajout effectué</t>
+  </si>
+  <si>
+    <t>Définition assez claire pour vous?</t>
+  </si>
+  <si>
+    <t>Définit l'accessibilité du point par un HBE (Hélicoptère bombardier d'eau)</t>
+  </si>
+  <si>
+    <t>ok pour vous?</t>
+  </si>
+  <si>
+    <t>validé par IGN</t>
+  </si>
+  <si>
+    <t>conserve</t>
+  </si>
+  <si>
+    <t>nom_gestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léger | Lourd | Non accessible </t>
+  </si>
+  <si>
+    <t>public | privé</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -790,8 +884,33 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -852,8 +971,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -917,37 +1042,9 @@
       <left style="thick">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -955,7 +1052,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -998,9 +1095,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1013,9 +1107,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1034,12 +1125,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1049,90 +1134,12 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1145,41 +1152,47 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1199,17 +1212,95 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1547,13 +1638,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5FE330-E567-4C63-B9B4-AD0BE082165A}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="250" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.5">
+    <row r="2" spans="1:3" ht="28">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1619,7 +1710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57">
+    <row r="7" spans="1:3" ht="56">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1641,7 +1732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="42.75">
+    <row r="9" spans="1:3" ht="42">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1663,7 +1754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.5">
+    <row r="11" spans="1:3" ht="28">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1674,7 +1765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="42.75">
+    <row r="12" spans="1:3" ht="42">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1881,52 +1972,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85754B1D-2531-463F-8465-85A5AC0ED493}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="30.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="29.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="36.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.58203125" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" customWidth="1"/>
+    <col min="6" max="6" width="26.25" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
+    <col min="8" max="8" width="36.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.58203125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="25.75" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="20" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="23.85546875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.58203125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="19.58203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="23.83203125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.58203125" customWidth="1"/>
+    <col min="18" max="18" width="16.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30.95" customHeight="1">
+    <row r="1" spans="1:18" ht="31" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78" t="s">
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="79"/>
-      <c r="J1" s="80" t="s">
+      <c r="I1" s="51"/>
+      <c r="J1" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="82"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="54"/>
       <c r="P1" s="10" t="s">
         <v>68</v>
       </c>
@@ -1988,28 +2079,28 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="60" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I3" s="8"/>
-      <c r="J3" s="19"/>
+      <c r="J3" s="18"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -2019,29 +2110,29 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
     </row>
-    <row r="4" spans="1:18" ht="90">
+    <row r="4" spans="1:18" ht="87">
       <c r="A4" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" s="22" t="s">
+      <c r="G4" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>83</v>
       </c>
       <c r="I4" s="8"/>
-      <c r="J4" s="19"/>
+      <c r="J4" s="18"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
@@ -2051,29 +2142,29 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
     </row>
-    <row r="5" spans="1:18" ht="75">
+    <row r="5" spans="1:18" ht="72.5">
       <c r="A5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="22" t="s">
+      <c r="G5" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I5" s="8"/>
-      <c r="J5" s="19"/>
+      <c r="J5" s="18"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
@@ -2083,29 +2174,29 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75">
+    <row r="6" spans="1:18" ht="15.5">
       <c r="A6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="23" t="s">
+      <c r="G6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="21" t="s">
         <v>87</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="19"/>
+      <c r="J6" s="18"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2115,46 +2206,46 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="45">
+    <row r="7" spans="1:18" ht="43.5">
       <c r="A7" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="24" t="s">
+      <c r="G7" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="22" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="19"/>
+      <c r="J7" s="18"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
-      <c r="M7" s="25"/>
+      <c r="M7" s="23"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:18" ht="105">
+    <row r="8" spans="1:18" ht="101.5">
       <c r="A8" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2164,14 +2255,14 @@
       <c r="F8" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="22" t="s">
+      <c r="G8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>93</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="19"/>
+      <c r="J8" s="18"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -2181,29 +2272,29 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" spans="1:18" ht="30">
+    <row r="9" spans="1:18" ht="29">
       <c r="A9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="26" t="s">
+      <c r="G9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="24" t="s">
         <v>95</v>
       </c>
       <c r="I9" s="8"/>
-      <c r="J9" s="19"/>
+      <c r="J9" s="18"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
@@ -2213,14 +2304,14 @@
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
     </row>
-    <row r="10" spans="1:18" ht="85.5">
+    <row r="10" spans="1:18" ht="84">
       <c r="A10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2230,14 +2321,14 @@
       <c r="F10" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="24" t="s">
+      <c r="G10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>99</v>
       </c>
       <c r="I10" s="8"/>
-      <c r="J10" s="19"/>
+      <c r="J10" s="18"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -2247,29 +2338,29 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:18" ht="30">
+    <row r="11" spans="1:18" ht="29">
       <c r="A11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="24" t="s">
+      <c r="G11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="22" t="s">
         <v>99</v>
       </c>
       <c r="I11" s="8"/>
-      <c r="J11" s="19"/>
+      <c r="J11" s="18"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -2279,14 +2370,14 @@
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
     </row>
-    <row r="12" spans="1:18" ht="60">
+    <row r="12" spans="1:18" ht="58">
       <c r="A12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2296,14 +2387,14 @@
       <c r="F12" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="24" t="s">
+      <c r="G12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>104</v>
       </c>
       <c r="I12" s="8"/>
-      <c r="J12" s="19"/>
+      <c r="J12" s="18"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
@@ -2313,14 +2404,14 @@
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
     </row>
-    <row r="13" spans="1:18" ht="71.25">
+    <row r="13" spans="1:18" ht="70">
       <c r="A13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2330,14 +2421,14 @@
       <c r="F13" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="26" t="s">
+      <c r="G13" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="24" t="s">
         <v>108</v>
       </c>
       <c r="I13" s="8"/>
-      <c r="J13" s="19"/>
+      <c r="J13" s="18"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -2347,29 +2438,29 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
     </row>
-    <row r="14" spans="1:18" ht="30">
+    <row r="14" spans="1:18" ht="29">
       <c r="A14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="24" t="s">
+      <c r="G14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>110</v>
       </c>
       <c r="I14" s="8"/>
-      <c r="J14" s="19"/>
+      <c r="J14" s="18"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
@@ -2383,25 +2474,25 @@
       <c r="A15" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="8"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="20" t="s">
+      <c r="F15" s="16"/>
+      <c r="G15" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>112</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="19"/>
+      <c r="J15" s="18"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2411,29 +2502,29 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="30">
+    <row r="16" spans="1:18" ht="29">
       <c r="A16" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="27" t="s">
+      <c r="G16" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="25" t="s">
         <v>114</v>
       </c>
       <c r="I16" s="8"/>
-      <c r="J16" s="19"/>
+      <c r="J16" s="18"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
@@ -2447,25 +2538,25 @@
       <c r="A17" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
-      <c r="G17" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="27" t="s">
+      <c r="G17" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>114</v>
       </c>
       <c r="I17" s="8"/>
-      <c r="J17" s="19"/>
+      <c r="J17" s="18"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
@@ -2475,29 +2566,29 @@
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
     </row>
-    <row r="18" spans="1:18" ht="30">
+    <row r="18" spans="1:18" ht="29">
       <c r="A18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="27" t="s">
+      <c r="G18" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="25" t="s">
         <v>114</v>
       </c>
       <c r="I18" s="8"/>
-      <c r="J18" s="19"/>
+      <c r="J18" s="18"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
@@ -2507,29 +2598,29 @@
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
     </row>
-    <row r="19" spans="1:18" ht="45">
+    <row r="19" spans="1:18" ht="43.5">
       <c r="A19" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>39</v>
       </c>
       <c r="E19" s="8"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="27" t="s">
+      <c r="F19" s="16"/>
+      <c r="G19" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="25" t="s">
         <v>118</v>
       </c>
       <c r="I19" s="8"/>
-      <c r="J19" s="19"/>
+      <c r="J19" s="18"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
@@ -2539,29 +2630,29 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" spans="1:18" ht="15.75">
+    <row r="20" spans="1:18" ht="15.5">
       <c r="A20" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>42</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="20" t="s">
+      <c r="F20" s="16"/>
+      <c r="G20" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>120</v>
       </c>
       <c r="I20" s="8"/>
-      <c r="J20" s="19"/>
+      <c r="J20" s="18"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
@@ -2571,27 +2662,27 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75">
+    <row r="21" spans="1:18" ht="15.5">
       <c r="A21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="19"/>
+      <c r="J21" s="18"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
@@ -2601,27 +2692,27 @@
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75">
+    <row r="22" spans="1:18" ht="15.5">
       <c r="A22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="19"/>
+      <c r="J22" s="18"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -2631,27 +2722,27 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75">
+    <row r="23" spans="1:18" ht="15.5">
       <c r="A23" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="19"/>
+      <c r="J23" s="18"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -2661,27 +2752,27 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
     </row>
-    <row r="24" spans="1:18" ht="15.75">
+    <row r="24" spans="1:18" ht="15.5">
       <c r="A24" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>51</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="19"/>
+      <c r="J24" s="18"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
@@ -2691,195 +2782,195 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" spans="1:18" ht="30">
+    <row r="25" spans="1:18" ht="29">
       <c r="A25" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:18" ht="15.75">
+    <row r="26" spans="1:18" ht="15.5">
       <c r="A26" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="G26" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" s="19" t="s">
+      <c r="G26" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:18" ht="15.75">
+    <row r="27" spans="1:18" ht="15.5">
       <c r="A27" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="19" t="s">
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:18" ht="15.75">
+    <row r="28" spans="1:18" ht="15.5">
       <c r="A28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="19" t="s">
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:18" ht="15.75">
+    <row r="29" spans="1:18" ht="15.5">
       <c r="A29" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H29" s="19" t="s">
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75">
+    <row r="30" spans="1:18" ht="15.5">
       <c r="A30" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H30" s="19" t="s">
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
@@ -2897,1448 +2988,1776 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}">
-  <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="87" customHeight="1"/>
+  <dimension ref="A1:Y37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="68.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="16" customWidth="1"/>
-    <col min="2" max="2" width="17" style="16" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="16" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="30" style="16" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="41" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="24.42578125" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10" style="41" customWidth="1"/>
-    <col min="12" max="13" width="10" style="16" customWidth="1"/>
-    <col min="14" max="14" width="34.42578125" style="16" customWidth="1"/>
-    <col min="15" max="15" width="13" style="16" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="16" customWidth="1"/>
-    <col min="17" max="17" width="30.42578125" style="16" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" style="16" customWidth="1"/>
-    <col min="19" max="16384" width="10.5703125" style="16"/>
+    <col min="1" max="1" width="13.58203125" style="64" customWidth="1"/>
+    <col min="2" max="2" width="17" style="64" customWidth="1"/>
+    <col min="3" max="3" width="9.4140625" style="64" customWidth="1"/>
+    <col min="4" max="4" width="38.75" style="64" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="64" customWidth="1"/>
+    <col min="6" max="6" width="30" style="64" customWidth="1"/>
+    <col min="7" max="7" width="17.4140625" style="64" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="79" customWidth="1"/>
+    <col min="9" max="9" width="11.58203125" style="64" customWidth="1"/>
+    <col min="10" max="10" width="12" style="64" customWidth="1"/>
+    <col min="11" max="11" width="19.4140625" style="80" customWidth="1"/>
+    <col min="12" max="12" width="24.6640625" style="81" customWidth="1"/>
+    <col min="13" max="13" width="17.58203125" style="81" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="82" customWidth="1"/>
+    <col min="15" max="15" width="34.4140625" style="83" customWidth="1"/>
+    <col min="16" max="16" width="26.6640625" style="65" customWidth="1"/>
+    <col min="17" max="17" width="30.4140625" style="81" customWidth="1"/>
+    <col min="18" max="18" width="30.4140625" style="83" customWidth="1"/>
+    <col min="19" max="19" width="15.4140625" style="81" customWidth="1"/>
+    <col min="20" max="20" width="16" style="65" customWidth="1"/>
+    <col min="21" max="21" width="40.83203125" style="84" customWidth="1"/>
+    <col min="22" max="22" width="10.58203125" style="65"/>
+    <col min="23" max="16384" width="10.58203125" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="87" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:25" s="40" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="85" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="84" t="s">
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="10" t="s">
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="42" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="87" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="T1" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="U1" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="V1" s="43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="68.5" customHeight="1">
+      <c r="A2" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="S2" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+    </row>
+    <row r="3" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A3" s="26"/>
+      <c r="B3" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="L3" s="37"/>
+      <c r="M3" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="S3" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="52" t="s">
+    </row>
+    <row r="4" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A4" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="26"/>
+      <c r="K4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="L4" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="N4" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="M2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="21" customFormat="1" ht="105">
-      <c r="A3" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="63" t="s">
+      <c r="O4" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="P4" s="66">
+        <v>27098</v>
+      </c>
+      <c r="Q4" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="S4" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A5" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="62" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="J3" s="67"/>
-      <c r="K3" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3" s="54"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55" t="s">
+      <c r="D5" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="M5" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="R5" s="26"/>
+      <c r="S5" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A6" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="K6" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="R3" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="21" customFormat="1" ht="60">
-      <c r="A4" s="70"/>
-      <c r="B4" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="K4" s="71" t="s">
+      <c r="R6" s="26"/>
+      <c r="S6" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T6" s="63"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="69" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A7" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R7" s="26"/>
+      <c r="S7" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="W7" s="68"/>
+      <c r="X7" s="68"/>
+      <c r="Y7" s="68"/>
+    </row>
+    <row r="8" spans="1:25" s="69" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A8" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L4" s="54"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="62" t="s">
+      <c r="N8" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O8" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R8" s="26"/>
+      <c r="S8" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+    </row>
+    <row r="9" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A9" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="N9" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="R9" s="32"/>
+      <c r="S9" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="T9" s="63"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="M10" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="N10" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="O10" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q10" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="R4" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="32" t="s">
+      <c r="R10" s="32"/>
+      <c r="S10" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="T10" s="63"/>
+      <c r="U10" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="V10" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A11" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T11" s="63"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="27"/>
+      <c r="J12" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T12" s="63"/>
+      <c r="U12" s="63"/>
+      <c r="V12" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A13" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="K5" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" s="32" t="s">
+      <c r="D13" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="K13" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A14" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="N5" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="R5" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="32" t="s">
+      <c r="N14" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O14" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="P14" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q14" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R14" s="26"/>
+      <c r="S14" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A15" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="31"/>
-      <c r="J6" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="M6" s="32" t="s">
+      <c r="D15" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="27"/>
+      <c r="J15" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="K15" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="26"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" s="73" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A17" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="27"/>
+      <c r="J17" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K17" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O17" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R17" s="26"/>
+      <c r="S17" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" s="73" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A18" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="27"/>
+      <c r="J18" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R18" s="26"/>
+      <c r="S18" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T18" s="67"/>
+      <c r="U18" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="V18" s="71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" s="73" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A19" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L19" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R19" s="26"/>
+      <c r="S19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T19" s="75" t="s">
+        <v>198</v>
+      </c>
+      <c r="U19" s="74"/>
+      <c r="V19" s="71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A20" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="27"/>
+      <c r="J20" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R20" s="26"/>
+      <c r="S20" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T20" s="63"/>
+      <c r="U20" s="63"/>
+      <c r="V20" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A21" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T21" s="63"/>
+      <c r="U21" s="63"/>
+      <c r="V21" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A22" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="63"/>
+      <c r="U22" s="63"/>
+      <c r="V22" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A23" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T23" s="63"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A24" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="R24" s="30"/>
+      <c r="S24" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A25" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T25" s="63"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A26" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T26" s="63"/>
+      <c r="U26" s="63"/>
+      <c r="V26" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="28"/>
+      <c r="J27" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="L27" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="M27" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="N27" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="O27" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q27" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R27" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="S27" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T27" s="63"/>
+      <c r="U27" s="63"/>
+      <c r="V27" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A28" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="28"/>
+      <c r="J28" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T28" s="63"/>
+      <c r="U28" s="63"/>
+      <c r="V28" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A29" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="28"/>
+      <c r="J29" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T29" s="63"/>
+      <c r="U29" s="63"/>
+      <c r="V29" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A30" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T30" s="63"/>
+      <c r="U30" s="63"/>
+      <c r="V30" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A31" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T31" s="63"/>
+      <c r="U31" s="63"/>
+      <c r="V31" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" s="65" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A32" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="K32" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="L32" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="M32" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="N6" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="O6" s="33"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="R6" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="33" customFormat="1" ht="87" customHeight="1">
-      <c r="A7" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="32" t="s">
+      <c r="N32" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O32" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="P32" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q32" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R32" s="26"/>
+      <c r="S32" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T32" s="63"/>
+      <c r="U32" s="63"/>
+      <c r="V32" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="68.5" customHeight="1">
+      <c r="A33" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="78"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="78" t="s">
+        <v>170</v>
+      </c>
+      <c r="K33" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="L33" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="M33" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="N33" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="O33" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="P33" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q33" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="R33" s="26"/>
+      <c r="S33" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="T33" s="63"/>
+      <c r="U33" s="63"/>
+      <c r="V33" s="71" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="68.5" customHeight="1">
+      <c r="A34" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="78"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="78" t="s">
+        <v>172</v>
+      </c>
+      <c r="K34" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="R7" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="33" customFormat="1" ht="87" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="21" customFormat="1" ht="150" customHeight="1">
-      <c r="A9" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="I9" s="64"/>
-      <c r="J9" s="67" t="s">
-        <v>156</v>
-      </c>
-      <c r="K9" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="L9" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="N9" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="O9" s="69"/>
-      <c r="P9" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q9" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="R9" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="21" customFormat="1" ht="274.5" customHeight="1">
-      <c r="A10" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="68" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="K10" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="M10" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="N10" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="O10" s="69"/>
-      <c r="P10" s="61" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="R10" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A11" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="31"/>
-      <c r="J11" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="N14" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="O14" s="33"/>
-      <c r="P14" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q14" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="R14" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A15" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="K15" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A16" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="30"/>
-      <c r="J16" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="31"/>
-      <c r="J17" s="36" t="s">
+      <c r="L34" s="59"/>
+      <c r="M34" s="59"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T34" s="63"/>
+      <c r="U34" s="63"/>
+      <c r="V34" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="68.5" customHeight="1">
+      <c r="A35" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="K17" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A18" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" s="69" customFormat="1" ht="87" customHeight="1">
-      <c r="A19" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="64"/>
-      <c r="J19" s="67" t="s">
-        <v>173</v>
-      </c>
-      <c r="K19" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="62" t="s">
+      <c r="B35" s="78"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="78" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="31"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="M20" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="N20" s="32" t="s">
+      <c r="K35" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L35" s="59"/>
+      <c r="M35" s="59"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="59"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T35" s="63"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="68.5" customHeight="1">
+      <c r="A36" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="O20" s="33"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="R20" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K22" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A24" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="63" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="68"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="67" t="s">
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="K24" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="57"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="R24" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" s="40"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" s="39"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A27" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="71" t="s">
-        <v>129</v>
-      </c>
-      <c r="I27" s="63"/>
-      <c r="J27" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="K27" s="71" t="s">
-        <v>179</v>
-      </c>
-      <c r="L27" s="57"/>
-      <c r="M27" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="N27" s="56"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="R27" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="32"/>
-      <c r="J29" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="K29" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I30" s="32"/>
-      <c r="J30" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="32"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="32"/>
-      <c r="J31" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="K31" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" s="21" customFormat="1" ht="87" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="K32" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="M32" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="N32" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="O32" s="33"/>
-      <c r="P32" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q32" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="R32" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="87" customHeight="1">
-      <c r="A33" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="K33" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="L33" s="59"/>
-      <c r="M33" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="N33" s="59"/>
-      <c r="O33" s="60"/>
-      <c r="P33" s="59"/>
-      <c r="Q33" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="R33" s="62" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="87" customHeight="1">
-      <c r="A34" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="K34" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="49"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="87" customHeight="1">
-      <c r="A35" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="K35" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="87" customHeight="1">
-      <c r="A36" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="K36" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="30" t="s">
-        <v>149</v>
-      </c>
+      <c r="K36" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="L36" s="59"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="60"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="59"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="68.5" customHeight="1">
+      <c r="U37" s="65"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R36" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}"/>
-  <mergeCells count="3">
+  <autoFilter ref="A2:S36" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}"/>
+  <mergeCells count="4">
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="K1:Q1"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="K1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -4346,15 +4765,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010054AA600EF525E845A794782CB692D6B7" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="45133187a599b4bba422c4e82da267ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4d568f87-b25f-475a-a26b-5a1bcde8677b" xmlns:ns3="a486f84b-88b9-4459-bbe1-3ce207c7425f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e130176ad47eb97b39a20183f2e8d36" ns2:_="" ns3:_="">
     <xsd:import namespace="4d568f87-b25f-475a-a26b-5a1bcde8677b"/>
@@ -4555,6 +4965,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4567,13 +4986,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66A699F4-533F-44A1-AA69-2E72F9825D97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77907F28-6908-4689-9B04-5CEA6B9E57A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4d568f87-b25f-475a-a26b-5a1bcde8677b"/>
+    <ds:schemaRef ds:uri="a486f84b-88b9-4459-bbe1-3ce207c7425f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77907F28-6908-4689-9B04-5CEA6B9E57A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66A699F4-533F-44A1-AA69-2E72F9825D97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0237B64-00E3-41F7-846C-65A87C6720AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0237B64-00E3-41F7-846C-65A87C6720AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a486f84b-88b9-4459-bbe1-3ce207c7425f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4d568f87-b25f-475a-a26b-5a1bcde8677b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>